--- a/data/ams_weekly_data/White_Mulberry/ads_report_week32.xlsx
+++ b/data/ams_weekly_data/White_Mulberry/ads_report_week32.xlsx
@@ -1,14 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SP" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SD" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="SP" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="SD" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="SB" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -18,16 +19,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -38,7 +36,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -46,21 +44,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -430,42 +419,42 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>Portfolio name</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>Campaign Name</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>Advertised ASIN</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>Spend</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>Clicks</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>Impressions</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>14 Day Total Sales (₹)</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>14 Day Total Units (#)</t>
         </is>
@@ -1137,10 +1126,10 @@
         <v>59800</v>
       </c>
       <c r="G25" t="n">
-        <v>3294.96</v>
+        <v>5073.78</v>
       </c>
       <c r="H25" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="26">
@@ -2033,10 +2022,10 @@
         <v>2030</v>
       </c>
       <c r="G57" t="n">
-        <v>0</v>
+        <v>3516.1</v>
       </c>
       <c r="H57" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="58">
@@ -2341,10 +2330,10 @@
         <v>38227</v>
       </c>
       <c r="G68" t="n">
-        <v>14066.11</v>
+        <v>21014.41</v>
       </c>
       <c r="H68" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="69">
@@ -2422,7 +2411,7 @@
         <v>18</v>
       </c>
       <c r="F71" t="n">
-        <v>9009</v>
+        <v>9008</v>
       </c>
       <c r="G71" t="n">
         <v>0</v>
@@ -2708,7 +2697,7 @@
         <v>8806.120000000001</v>
       </c>
       <c r="H81" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="82">
@@ -2954,7 +2943,7 @@
         <v>111</v>
       </c>
       <c r="F90" t="n">
-        <v>21324</v>
+        <v>21323</v>
       </c>
       <c r="G90" t="n">
         <v>6683.1</v>
@@ -3013,10 +3002,10 @@
         <v>32180</v>
       </c>
       <c r="G92" t="n">
-        <v>14094.67</v>
+        <v>15695.57</v>
       </c>
       <c r="H92" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="93">
@@ -3286,42 +3275,42 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>Portfolio name</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>Campaign Name</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>Advertised ASIN</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>Spend</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>Clicks</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>Impressions</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>14 Day Total Sales (₹)</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>14 Day Total Units (#)</t>
         </is>
@@ -4137,6 +4126,463 @@
       </c>
       <c r="H30" t="n">
         <v>0</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:I13"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Portfolio name</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Campaign Name</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>Advertised ASIN</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>Impressions</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>Clicks</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>Spend</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>14 Day Total Sales (₹)</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>14 Day Total Units (#)</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>Brand</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr"/>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Camb-SB-Multiple Asin- Product collection- exact /Reach</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>B0BFVMDJ2K</t>
+        </is>
+      </c>
+      <c r="D2" t="n">
+        <v>1746</v>
+      </c>
+      <c r="E2" t="n">
+        <v>64</v>
+      </c>
+      <c r="F2" t="n">
+        <v>188.2833541002838</v>
+      </c>
+      <c r="G2" t="n">
+        <v>7473.771893755647</v>
+      </c>
+      <c r="H2" t="n">
+        <v>1</v>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>White Mulberry</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr"/>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Camb-SB-Multiple Asin- Product collection- exact /Reach</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>B0CPFS24ML</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>5302</v>
+      </c>
+      <c r="E3" t="n">
+        <v>196</v>
+      </c>
+      <c r="F3" t="n">
+        <v>571.6566458997163</v>
+      </c>
+      <c r="G3" t="n">
+        <v>22691.49810624435</v>
+      </c>
+      <c r="H3" t="n">
+        <v>4</v>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>White Mulberry</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr"/>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Camb-SP-Zshape-B0CPFS24ML- SBV- Phrase</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>B0CPFS24ML</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>37029</v>
+      </c>
+      <c r="E4" t="n">
+        <v>118</v>
+      </c>
+      <c r="F4" t="n">
+        <v>1072.37</v>
+      </c>
+      <c r="G4" t="n">
+        <v>6948.31</v>
+      </c>
+      <c r="H4" t="n">
+        <v>1</v>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>White Mulberry</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr"/>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>SB-L shape-Multi Asin- KT- phrase</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>B0BFVMDJ2K</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>9453</v>
+      </c>
+      <c r="E5" t="n">
+        <v>61</v>
+      </c>
+      <c r="F5" t="n">
+        <v>449.6244354040174</v>
+      </c>
+      <c r="G5" t="n">
+        <v>6634.75</v>
+      </c>
+      <c r="H5" t="n">
+        <v>1</v>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>White Mulberry</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr"/>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>SB-L shape-Multi Asin- KT- phrase</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>B0BFWD6SNF</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>30059</v>
+      </c>
+      <c r="E6" t="n">
+        <v>194</v>
+      </c>
+      <c r="F6" t="n">
+        <v>1429.735564595983</v>
+      </c>
+      <c r="G6" t="n">
+        <v>21097.47</v>
+      </c>
+      <c r="H6" t="n">
+        <v>3</v>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>White Mulberry</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr"/>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>WM- SBV- Monitor Arm- Product Collection- Phrase</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>B0DB5VG39T</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>18411</v>
+      </c>
+      <c r="E7" t="n">
+        <v>77</v>
+      </c>
+      <c r="F7" t="n">
+        <v>1465.408856116154</v>
+      </c>
+      <c r="G7" t="n">
+        <v>5598.88846779503</v>
+      </c>
+      <c r="H7" t="n">
+        <v>2</v>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>White Mulberry</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr"/>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>WM- SBV- Monitor Arm- Product Collection- Phrase</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>B0DP32F346</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>13708</v>
+      </c>
+      <c r="E8" t="n">
+        <v>58</v>
+      </c>
+      <c r="F8" t="n">
+        <v>1091.041143883846</v>
+      </c>
+      <c r="G8" t="n">
+        <v>4168.54153220497</v>
+      </c>
+      <c r="H8" t="n">
+        <v>2</v>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>White Mulberry</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr"/>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>WM-SB-Monitor Arms-Branded</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>B0DB5VG39T</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>205</v>
+      </c>
+      <c r="E9" t="n">
+        <v>8</v>
+      </c>
+      <c r="F9" t="n">
+        <v>64.67999999999999</v>
+      </c>
+      <c r="G9" t="n">
+        <v>2329.66</v>
+      </c>
+      <c r="H9" t="n">
+        <v>1</v>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>White Mulberry</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr"/>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>WM-SBV-Gas Spring MA- B0DB5VG39T- BM</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>B0DB5VG39T</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>2463</v>
+      </c>
+      <c r="E10" t="n">
+        <v>24</v>
+      </c>
+      <c r="F10" t="n">
+        <v>454.03</v>
+      </c>
+      <c r="G10" t="n">
+        <v>0</v>
+      </c>
+      <c r="H10" t="n">
+        <v>0</v>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>White Mulberry</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr"/>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>WM-SBV-Gas Spring MA- B0DB5VG39T- Phrase</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>B0DB5VG39T</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>20187</v>
+      </c>
+      <c r="E11" t="n">
+        <v>217</v>
+      </c>
+      <c r="F11" t="n">
+        <v>2844.52</v>
+      </c>
+      <c r="G11" t="n">
+        <v>4659.32</v>
+      </c>
+      <c r="H11" t="n">
+        <v>2</v>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>White Mulberry</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr"/>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>White Mulberry Monitor Arm-B0DB5VG39T-CT-SBV</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>B0DB5VG39T</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>10758</v>
+      </c>
+      <c r="E12" t="n">
+        <v>161</v>
+      </c>
+      <c r="F12" t="n">
+        <v>1487.009290234967</v>
+      </c>
+      <c r="G12" t="n">
+        <v>6732.72</v>
+      </c>
+      <c r="H12" t="n">
+        <v>3</v>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>White Mulberry</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr"/>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>White Mulberry Monitor Arm-B0DB5VG39T-CT-SBV</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>B0DP32F346</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>8162</v>
+      </c>
+      <c r="E13" t="n">
+        <v>123</v>
+      </c>
+      <c r="F13" t="n">
+        <v>1128.190709765033</v>
+      </c>
+      <c r="G13" t="n">
+        <v>5108.1</v>
+      </c>
+      <c r="H13" t="n">
+        <v>3</v>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>White Mulberry</t>
+        </is>
       </c>
     </row>
   </sheetData>
